--- a/data/trans_dic/IP31KM13_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM13_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>90,03; 100,0</t>
+          <t>84,95; 97,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>81,45; 96,48</t>
+          <t>90,19; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,97; 97,34</t>
+          <t>90,89; 97,77</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>90,37; 96,4</t>
+          <t>85,27; 93,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,66; 94,2</t>
+          <t>90,33; 96,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,34; 94,3</t>
+          <t>88,82; 93,94</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,34%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,02; 94,43</t>
+          <t>88,41; 96,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,17; 95,87</t>
+          <t>88,27; 95,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,11; 94,3</t>
+          <t>89,32; 94,54</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,08; 94,67</t>
+          <t>81,25; 94,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75,42; 94,38</t>
+          <t>86,75; 93,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83,8; 93,68</t>
+          <t>85,06; 92,95</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,63%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,8; 93,96</t>
+          <t>86,75; 93,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85,79; 93,42</t>
+          <t>90,18; 93,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,21; 93,17</t>
+          <t>89,57; 93,07</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>81</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45257</t>
+          <t>34841</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41366</t>
+          <t>41573</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86622</t>
+          <t>76414</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41861; 46495</t>
+          <t>31800; 36429</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36886; 43689</t>
+          <t>38493; 42681</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81651; 89337</t>
+          <t>72816; 78330</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>239</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>149485</t>
+          <t>141621</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>165420</t>
+          <t>136242</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>314906</t>
+          <t>277863</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>143963; 153567</t>
+          <t>133914; 147206</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>157684; 171407</t>
+          <t>131444; 139902</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>304886; 321821</t>
+          <t>268729; 284220</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>216</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>157325</t>
+          <t>185070</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>197515</t>
+          <t>161017</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>354840</t>
+          <t>346086</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>145407; 163428</t>
+          <t>176922; 192168</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>189477; 203717</t>
+          <t>154176; 166159</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>339729; 363572</t>
+          <t>334772; 354346</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>310</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>251086</t>
+          <t>264480</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>274892</t>
+          <t>230972</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>525978</t>
+          <t>495452</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>241564; 259642</t>
+          <t>237418; 275330</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>230030; 287866</t>
+          <t>221516; 239497</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>485419; 542667</t>
+          <t>465779; 508950</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>846</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>869</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>603153</t>
+          <t>626011</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>679193</t>
+          <t>569803</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1282346</t>
+          <t>1195814</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>586492; 613665</t>
+          <t>595829; 640733</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>638897; 695737</t>
+          <t>557527; 579751</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1247065; 1302456</t>
+          <t>1168873; 1214604</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM13_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM13_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que desayunan lácteos (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>93,07%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>95,38%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>84,95; 97,31</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>90,19; 100,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>90,89; 97,77</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>90,18%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>93,63%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>91,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>85,27; 93,74</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>90,33; 96,14</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>88,82; 93,94</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>92,48%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>92,18%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>92,34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>88,41; 96,02</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>88,27; 95,13</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>89,32; 94,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>90,51%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>90,46%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>90,48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>81,25; 94,22</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>86,75; 93,8</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>85,06; 92,95</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>91,15%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>86,75; 93,29</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>90,18; 93,78</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>89,57; 93,07</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9307044111322269</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9740447346409612</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9537934319799619</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>34841</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>41573</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>76414</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.8494635483103607</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.9018689261035259</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.9088779861039352</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>31800; 36429</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>38493; 42681</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>72816; 78330</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9731292915339398</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9777053021818387</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>490</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9018007056626843</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.936254800469148</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9183715817604202</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>141621</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>136242</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>277863</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8527276153182796</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.9032835227072462</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8881851860000414</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>133914; 147206</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>131444; 139902</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>268729; 284220</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9373650566737766</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9614052182232828</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9393831316376965</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.924766271688056</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9218226632539208</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9233944216673355</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>185070</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>161017</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>346086</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.8840528046064852</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.8826579633477654</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.8932061998992272</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>176922; 192168</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>154176; 166159</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>334772; 354346</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9602334793349747</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9512601263452953</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9454326094505884</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9050686411181635</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9045755107316005</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9048386846355483</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>264480</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>230972</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>495452</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8124614098442176</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.8675429972936223</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.8506485251274836</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>237418; 275330</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>221516; 239497</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>465779; 508950</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9421974628138338</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.93796622145778</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9294911932559475</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>869</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>846</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1715</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.9114581644351256</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9217016123661534</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9163105981526873</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>626011</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>569803</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1195814</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8675134355668738</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.901844322994351</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.8956665053641897</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>595829; 640733</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>557527; 579751</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1168873; 1214604</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9328919465149366</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.9377933183047676</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9307088302404574</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que desayunan lácteos (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>34841</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>41573</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>76414</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>31800</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>38493</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>72816</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>36429</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>42681</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>78330</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>251</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>239</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>141621</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>136242</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>277863</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>133914</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>131444</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>268729</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>147206</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>139902</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>284220</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>227</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>216</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>185070</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>161017</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>346086</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>176922</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>154176</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>334772</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>192168</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>166159</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>354346</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>317</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>310</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>264480</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>230972</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>495452</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>237418</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>221516</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>465779</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>275330</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>239497</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>508950</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>869</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>846</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>626011</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>569803</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1195814</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>595829</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>557527</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1168873</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>640733</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>579751</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1214604</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>